--- a/data/availability/projects/hassan-allam-properties/swanlake-west.xlsx
+++ b/data/availability/projects/hassan-allam-properties/swanlake-west.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1159,7 +1159,6 @@
       <c r="G2" t="n">
         <v>151</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1192,7 +1191,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1216,7 +1215,6 @@
       <c r="G3" t="n">
         <v>190</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1249,7 +1247,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1310,7 +1308,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1334,7 +1332,6 @@
       <c r="G5" t="n">
         <v>348</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1367,7 +1364,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1428,7 +1425,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1452,7 +1449,6 @@
       <c r="G7" t="n">
         <v>373</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/hassan-allam-properties/swanlake-west.xlsx
+++ b/data/availability/projects/hassan-allam-properties/swanlake-west.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
